--- a/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
+++ b/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
+++ b/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>BANDERA DEL PERU</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.71081</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.20735999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1824</v>
-      </c>
-      <c r="J2" t="n">
-        <v>91</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.71081</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.20736</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.7173</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.2183</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1801</v>
-      </c>
-      <c r="J3" t="n">
-        <v>98</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.7173</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.2183</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>22454 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.7042</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.20282</v>
-      </c>
-      <c r="I4" t="n">
-        <v>675</v>
-      </c>
-      <c r="J4" t="n">
-        <v>37</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.7042</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.20282</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>22469</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.70046</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.15345000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>649</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.70046</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.15345</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>182</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.7116</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.20699</v>
-      </c>
-      <c r="I6" t="n">
-        <v>648</v>
-      </c>
-      <c r="J6" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.7116</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.20699</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>189</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.70547</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.19877</v>
-      </c>
-      <c r="I7" t="n">
-        <v>203</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.70547</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.19877</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>22455 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.71073</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.20891</v>
-      </c>
-      <c r="I8" t="n">
-        <v>889</v>
-      </c>
-      <c r="J8" t="n">
-        <v>34</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.71073</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.20891</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>22459 JULIO C. TELLO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.7116</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.20596999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>833</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.7116</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.20597</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>22460</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.70885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.21516</v>
-      </c>
-      <c r="I10" t="n">
-        <v>280</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.70885</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.21516</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>22462 HILDA BRINGAS QUINTANILLA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.71314</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.19878</v>
-      </c>
-      <c r="I11" t="n">
-        <v>648</v>
-      </c>
-      <c r="J11" t="n">
-        <v>27</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.71314</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.19878</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>22464 REPUBLICA ARGENTINA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.71165</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.20753999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>734</v>
-      </c>
-      <c r="J12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.71165</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.20754</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>22488 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.71278</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.20731000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>516</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.71278</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.20731</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.70951</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.20935</v>
-      </c>
-      <c r="I14" t="n">
-        <v>377</v>
-      </c>
-      <c r="J14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.70951</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.20935</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>22544 PEDRO PABLO CASTRO PELAEZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.70947</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.20985</v>
-      </c>
-      <c r="I15" t="n">
-        <v>240</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.70947</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.20985</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>22646 CARLOS M. MEDRANO VASQUEZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.721402</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.20116</v>
-      </c>
-      <c r="I16" t="n">
-        <v>206</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.721402</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.20116</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.71499</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.19714</v>
-      </c>
-      <c r="I17" t="n">
-        <v>610</v>
-      </c>
-      <c r="J17" t="n">
-        <v>35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.71499</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.19714</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SANTA LUISA DE MARILLAC</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.70864</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.20712</v>
-      </c>
-      <c r="I18" t="n">
-        <v>807</v>
-      </c>
-      <c r="J18" t="n">
-        <v>43</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.70864</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.20712</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.70853</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.20085</v>
-      </c>
-      <c r="I19" t="n">
-        <v>322</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.70853</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.20085</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.71145</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.20201</v>
-      </c>
-      <c r="I20" t="n">
-        <v>217</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.71145</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.20201</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.71497</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.20571</v>
-      </c>
-      <c r="I21" t="n">
-        <v>213</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.71497</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.20571</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>ANTONIO RAIMONDI SAC</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.71683</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.19917</v>
-      </c>
-      <c r="I22" t="n">
-        <v>599</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.71683</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.19917</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.70961</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.20874000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>355</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.70961</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.20874</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.74312</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.96709</v>
-      </c>
-      <c r="I24" t="n">
-        <v>374</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.74312</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.96709</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>22552 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.609637</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.03983700000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>220</v>
-      </c>
-      <c r="J25" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.609637</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.039837</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>22697</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-13.726878</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.183148</v>
-      </c>
-      <c r="I26" t="n">
-        <v>80</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-13.726878</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.183148</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>NUESTRO SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.71766</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.19595</v>
-      </c>
-      <c r="I27" t="n">
-        <v>6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.71766</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.19595</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>EMILIA BARCIA BONIFATTI</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-13.71571</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.21174999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>327</v>
-      </c>
-      <c r="J28" t="n">
-        <v>38</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-13.71571</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.21175</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>22777 NUESTRA SEÑORA DE LAS AMERICAS DE COPRODELI</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-13.706238</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.194945</v>
-      </c>
-      <c r="I29" t="n">
-        <v>697</v>
-      </c>
-      <c r="J29" t="n">
-        <v>33</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-13.706238</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.194945</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>PROLOG DE PISCO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-13.71294</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.2132</v>
-      </c>
-      <c r="I30" t="n">
-        <v>259</v>
-      </c>
-      <c r="J30" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-13.71294</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.2132</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-13.7444</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-75.96708</v>
-      </c>
-      <c r="I31" t="n">
-        <v>310</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-13.7444</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-75.96708</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-13.71027</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.21107000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>372</v>
-      </c>
-      <c r="J32" t="n">
-        <v>36</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-13.71027</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.21107</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>907</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-13.71718</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.19602</v>
-      </c>
-      <c r="I33" t="n">
-        <v>77</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-13.71718</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.19602</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
+++ b/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>218103</t>
+          <t>505585</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BANDERA DEL PERU</t>
+          <t>NUESTRO SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.71081</t>
+          <t>-13.71766</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.20736</t>
+          <t>-76.19595</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>218117</t>
+          <t>218179</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.7173</t>
+          <t>-13.70547</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.2183</t>
+          <t>-76.19877</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>218122</t>
+          <t>218344</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22454 MIGUEL GRAU SEMINARIO</t>
+          <t>22544 PEDRO PABLO CASTRO PELAEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.7042</t>
+          <t>-13.70947</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.20282</t>
+          <t>-76.20985</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>218136</t>
+          <t>590201</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>PROLOG DE PISCO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.70046</t>
+          <t>-13.71294</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.15345</t>
+          <t>-76.2132</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>218155</t>
+          <t>218508</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.7116</t>
+          <t>-13.71497</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.20699</t>
+          <t>-76.20571</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>218179</t>
+          <t>218933</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.70547</t>
+          <t>-13.74312</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.19877</t>
+          <t>-75.96709</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>374</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>218259</t>
+          <t>218283</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22455 JOSE DE LA TORRE UGARTE</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.71073</t>
+          <t>-13.70885</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.20891</t>
+          <t>-76.21516</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>218278</t>
+          <t>218339</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22459 JULIO C. TELLO</t>
+          <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.7116</t>
+          <t>-13.70951</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.20597</t>
+          <t>-76.20935</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>218283</t>
+          <t>219188</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>22552 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.70885</t>
+          <t>-13.609637</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.21516</t>
+          <t>-76.039837</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>218297</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22462 HILDA BRINGAS QUINTANILLA</t>
+          <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.71314</t>
+          <t>-13.71145</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.19878</t>
+          <t>-76.20201</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>218315</t>
+          <t>623895</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22464 REPUBLICA ARGENTINA</t>
+          <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.71165</t>
+          <t>-13.7444</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.20754</t>
+          <t>-75.96708</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>218339</t>
+          <t>218155</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.70951</t>
+          <t>-13.7116</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.20935</t>
+          <t>-76.20699</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>648</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>218344</t>
+          <t>218749</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22544 PEDRO PABLO CASTRO PELAEZ</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.70947</t>
+          <t>-13.70961</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.20985</t>
+          <t>-76.20874</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>218363</t>
+          <t>218297</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22646 CARLOS M. MEDRANO VASQUEZ</t>
+          <t>22462 HILDA BRINGAS QUINTANILLA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.721402</t>
+          <t>-13.71314</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.20116</t>
+          <t>-76.19878</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>648</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>218396</t>
+          <t>218315</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RAUL PORRAS BARRENECHEA</t>
+          <t>22464 REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.71499</t>
+          <t>-13.71165</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.19714</t>
+          <t>-76.20754</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>734</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>218688</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA LUISA DE MARILLAC</t>
+          <t>ANTONIO RAIMONDI SAC</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.70864</t>
+          <t>-13.71683</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.20712</t>
+          <t>-76.19917</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>599</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>218443</t>
+          <t>760401</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>907</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.70853</t>
+          <t>-13.71718</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.20085</t>
+          <t>-76.19602</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>218476</t>
+          <t>218443</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LIBERTADOR SIMON BOLIVAR</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.71145</t>
+          <t>-13.70853</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.20201</t>
+          <t>-76.20085</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>218278</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>22459 JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.71497</t>
+          <t>-13.7116</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.20571</t>
+          <t>-76.20597</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>833</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>218688</t>
+          <t>571269</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI SAC</t>
+          <t>22777 NUESTRA SEÑORA DE LAS AMERICAS DE COPRODELI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.71683</t>
+          <t>-13.706238</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.19917</t>
+          <t>-76.194945</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>697</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>218749</t>
+          <t>218259</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>22455 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.70961</t>
+          <t>-13.71073</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.20874</t>
+          <t>-76.20891</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>889</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>218933</t>
+          <t>218396</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JUAN VELAZCO ALVARADO</t>
+          <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.74312</t>
+          <t>-13.71499</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.96709</t>
+          <t>-76.19714</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>610</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>219188</t>
+          <t>639518</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>22552 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.609637</t>
+          <t>-13.71027</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.039837</t>
+          <t>-76.21107</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>219334</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>22454 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.726878</t>
+          <t>-13.7042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.183148</t>
+          <t>-76.20282</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>675</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>505585</t>
+          <t>218136</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRO SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.71766</t>
+          <t>-13.70046</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.19595</t>
+          <t>-76.15345</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>649</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>571269</t>
+          <t>218419</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22777 NUESTRA SEÑORA DE LAS AMERICAS DE COPRODELI</t>
+          <t>SANTA LUISA DE MARILLAC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.706238</t>
+          <t>-13.70864</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.194945</t>
+          <t>-76.20712</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>807</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>590201</t>
+          <t>218363</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PROLOG DE PISCO</t>
+          <t>22646 CARLOS M. MEDRANO VASQUEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.71294</t>
+          <t>-13.721402</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.2132</t>
+          <t>-76.20116</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>623895</t>
+          <t>218103</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JUAN VELAZCO ALVARADO</t>
+          <t>BANDERA DEL PERU</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.7444</t>
+          <t>-13.71081</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.96708</t>
+          <t>-76.20736</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>639518</t>
+          <t>218117</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.71027</t>
+          <t>-13.7173</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.21107</t>
+          <t>-76.2183</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2395,68 +2395,6 @@
         </is>
       </c>
       <c r="L32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>110501</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>PISCO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PISCO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>760401</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-13.71718</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-76.19602</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
+++ b/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>505585</t>
+          <t>760401</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NUESTRO SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>907</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.71766</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.19595</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-13.71718</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>-76.19602</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>218179</t>
+          <t>639518</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.70547</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.19877</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-13.71027</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.21107</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>218344</t>
+          <t>623895</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22544 PEDRO PABLO CASTRO PELAEZ</t>
+          <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.70947</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.20985</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-13.7444</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.96708</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-13.71294</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-76.2132</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>571269</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>22777 NUESTRA SEÑORA DE LAS AMERICAS DE COPRODELI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.71497</t>
+          <t>697</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.20571</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-13.706238</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.194945</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>218933</t>
+          <t>549184</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JUAN VELAZCO ALVARADO</t>
+          <t>EMILIA BARCIA BONIFATTI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.74312</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.96709</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>-13.71571</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.21175</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>218283</t>
+          <t>505585</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>NUESTRO SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.70885</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.21516</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-13.71766</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.19595</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>218339</t>
+          <t>219188</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>22552 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.70951</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.20935</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-13.609637</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.039837</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>219188</t>
+          <t>218933</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22552 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>JUAN VELAZCO ALVARADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.609637</t>
+          <t>374</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.039837</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-13.74312</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.96709</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>218476</t>
+          <t>218749</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LIBERTADOR SIMON BOLIVAR</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.71145</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.20201</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-13.70961</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.20874</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>623895</t>
+          <t>218688</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JUAN VELAZCO ALVARADO</t>
+          <t>ANTONIO RAIMONDI SAC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.7444</t>
+          <t>599</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.96708</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-13.71683</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.19917</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>218320</t>
+          <t>218508</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22488 JORGE CHAVEZ DARTNELL</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.71278</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.20731</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-13.71497</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.20571</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>218155</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.7116</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.20699</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>-13.71145</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.20201</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>218749</t>
+          <t>218443</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.70961</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.20874</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-13.70853</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.20085</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>218297</t>
+          <t>218419</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22462 HILDA BRINGAS QUINTANILLA</t>
+          <t>SANTA LUISA DE MARILLAC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.71314</t>
+          <t>807</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.19878</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>-13.70864</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.20712</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>218315</t>
+          <t>218396</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22464 REPUBLICA ARGENTINA</t>
+          <t>RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.71165</t>
+          <t>610</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.20754</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>-13.71499</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.19714</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>218688</t>
+          <t>218363</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI SAC</t>
+          <t>22646 CARLOS M. MEDRANO VASQUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.71683</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.19917</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>-13.721402</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.20116</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>760401</t>
+          <t>218344</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>22544 PEDRO PABLO CASTRO PELAEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.71718</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.19602</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-13.70947</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.20985</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>218443</t>
+          <t>218339</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>22540 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.70853</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.20085</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-13.70951</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.20935</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>218278</t>
+          <t>218320</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22459 JULIO C. TELLO</t>
+          <t>22488 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.7116</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.20597</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>-13.71278</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.20731</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>571269</t>
+          <t>218315</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22777 NUESTRA SEÑORA DE LAS AMERICAS DE COPRODELI</t>
+          <t>22464 REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.706238</t>
+          <t>734</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.194945</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>-13.71165</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.20754</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>218259</t>
+          <t>218297</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22455 JOSE DE LA TORRE UGARTE</t>
+          <t>22462 HILDA BRINGAS QUINTANILLA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.71073</t>
+          <t>648</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.20891</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>-13.71314</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.19878</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>218396</t>
+          <t>218283</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RAUL PORRAS BARRENECHEA</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.71499</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.19714</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>-13.70885</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.21516</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>639518</t>
+          <t>218278</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>22459 JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.71027</t>
+          <t>833</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.21107</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-13.7116</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-76.20597</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>218122</t>
+          <t>218259</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>22454 MIGUEL GRAU SEMINARIO</t>
+          <t>22455 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.7042</t>
+          <t>889</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.20282</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>-13.71073</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.20891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>218136</t>
+          <t>218179</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.70046</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.15345</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>-13.70547</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.19877</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>549184</t>
+          <t>218155</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EMILIA BARCIA BONIFATTI</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.71571</t>
+          <t>648</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.21175</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-13.7116</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.20699</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>218136</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA LUISA DE MARILLAC</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.70864</t>
+          <t>649</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.20712</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>-13.70046</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.15345</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>218363</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>22646 CARLOS M. MEDRANO VASQUEZ</t>
+          <t>22454 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.721402</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.20116</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-13.7042</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.20282</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>218103</t>
+          <t>218117</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BANDERA DEL PERU</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.71081</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.20736</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>-13.7173</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-76.2183</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>218117</t>
+          <t>218103</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>BANDERA DEL PERU</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.7173</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.2183</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>-13.71081</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>-76.20736</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
+++ b/ZonasEscolares/excels/ICA-PISCO-PISCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
